--- a/output/laminas_comunales/comunal_i_peringr_median_a_2022_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2022_magallanes_y_la_antartica_chilena.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>10.09</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>9.35</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>9.19</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>9.15</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>8.279999999999999</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>8.210000000000001</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>7.78</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>7.68</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>5.51</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -512,9 +480,6 @@
       </c>
       <c r="B11">
         <v>4.8</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
